--- a/results/Int Task Remove ACC 0.1/Rando_7_permute.xlsx
+++ b/results/Int Task Remove ACC 0.1/Rando_7_permute.xlsx
@@ -440,127 +440,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6275605422716888</v>
+        <v>0.6487876248242163</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6219619596869274</v>
+        <v>0.6464140661963074</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6219619596869274</v>
+        <v>0.647678288699468</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6066560713821328</v>
+        <v>0.6493424294706983</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5990450585508754</v>
+        <v>0.6647966481167237</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.597419707666302</v>
+        <v>0.6728075792160509</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5943946428434844</v>
+        <v>0.6676217538055065</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5944785054857641</v>
+        <v>0.6634357240651365</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5650856054554971</v>
+        <v>0.6646160839260173</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5596162314368539</v>
+        <v>0.6641000691661922</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5615770328905458</v>
+        <v>0.6580177056710814</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5344161903523542</v>
+        <v>0.6402672350022454</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5221804396259999</v>
+        <v>0.6224845304839339</v>
       </c>
     </row>
     <row r="15">
@@ -570,437 +570,437 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5166332126658268</v>
+        <v>0.6414088049764692</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5297075898149777</v>
+        <v>0.6385320704948825</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5371571602306414</v>
+        <v>0.6421182228331478</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5368411046048512</v>
+        <v>0.6462397848745667</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5261596810269377</v>
+        <v>0.6608168603793542</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5151824162712102</v>
+        <v>0.6279667434087242</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5144664423773502</v>
+        <v>0.6157760654379925</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5125184798298053</v>
+        <v>0.601198716764989</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.507925975784184</v>
+        <v>0.5942777268470816</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5084419905440091</v>
+        <v>0.5982831923967451</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5090741017955893</v>
+        <v>0.6291725079136832</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5011404773013602</v>
+        <v>0.6321137100942211</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5006438574848637</v>
+        <v>0.6321137100942211</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5045526214861007</v>
+        <v>0.6380474700798853</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5070682275862748</v>
+        <v>0.5883753812062453</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5151758602340287</v>
+        <v>0.5958058298467963</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.508641949678044</v>
+        <v>0.5847182051318474</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5028690857715418</v>
+        <v>0.5851503572493928</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4884400674397691</v>
+        <v>0.5864468136020289</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4929099189564537</v>
+        <v>0.5901039896764269</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4921163652892797</v>
+        <v>0.5901039896764269</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4945415527099926</v>
+        <v>0.5611497978008866</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4995468139298307</v>
+        <v>0.5790485988109534</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4967798930710335</v>
+        <v>0.5598918581666916</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4979411311568018</v>
+        <v>0.5604401067759923</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5051005969271853</v>
+        <v>0.5370918730270426</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5051005969271853</v>
+        <v>0.5389882067817834</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5014693718332974</v>
+        <v>0.5378723146198536</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4999147715166408</v>
+        <v>0.5376403948045591</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4771978295146238</v>
+        <v>0.5863249805777399</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4876536161462084</v>
+        <v>0.5765982799143781</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4904399319483341</v>
+        <v>0.5460250200232303</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.504984773603646</v>
+        <v>0.5551127802296143</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5009405181673253</v>
+        <v>0.5376332924309458</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4949354612773127</v>
+        <v>0.5128651302957756</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4533576198088478</v>
+        <v>0.5126007034627895</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4212171938631121</v>
+        <v>0.522779224355241</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4088784587193656</v>
+        <v>0.5323190779589309</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4096654563493581</v>
+        <v>0.5255013456266315</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4188826982900762</v>
+        <v>0.5032613553295665</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4444832039790775</v>
+        <v>0.4983137326032822</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4292415102050182</v>
+        <v>0.4981591193930858</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4168637120063987</v>
+        <v>0.5288296271690922</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.3904568137440764</v>
+        <v>0.5366080921166931</v>
       </c>
     </row>
     <row r="59">
@@ -1010,317 +1010,317 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.3687656183927438</v>
+        <v>0.546806281120689</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.3695460599855549</v>
+        <v>0.546806281120689</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.3706682350164502</v>
+        <v>0.5408269020429705</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.3672298666829839</v>
+        <v>0.5331708164560904</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.3552585427896157</v>
+        <v>0.5411557965749076</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.3935337805279139</v>
+        <v>0.5576035280221419</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4351949383022268</v>
+        <v>0.5015969413901202</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4351949383022268</v>
+        <v>0.5015969413901202</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.459589406318053</v>
+        <v>0.4826478085899384</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5136802642520053</v>
+        <v>0.4907300365936142</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5128159600169145</v>
+        <v>0.4930844734464104</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5262836993969539</v>
+        <v>0.4970383102032699</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5259676437711638</v>
+        <v>0.490149554134838</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5176343741770807</v>
+        <v>0.4879500036604541</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5148415023377736</v>
+        <v>0.4781271477850975</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5004321521175453</v>
+        <v>0.4779853734810481</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5004321521175453</v>
+        <v>0.4768372474696428</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5004321521175453</v>
+        <v>0.4785013882408732</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5004321521175453</v>
+        <v>0.4980323693409107</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5004321521175453</v>
+        <v>0.5002769925709172</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5004321521175453</v>
+        <v>0.5047340051814547</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5004321521175453</v>
+        <v>0.5047340051814547</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5004321521175453</v>
+        <v>0.506888482900216</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5004321521175453</v>
+        <v>0.5066497338795241</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5</v>
+        <v>0.4987486164029865</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5004321521175453</v>
+        <v>0.4987486164029865</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5004321521175453</v>
+        <v>0.4965684608719311</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5</v>
+        <v>0.4955041975028054</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5004321521175453</v>
+        <v>0.4998645085649162</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5004321521175453</v>
+        <v>0.5001160964917553</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5004321521175453</v>
+        <v>0.5002321929835104</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5004321521175453</v>
+        <v>0.5001160964917553</v>
       </c>
     </row>
   </sheetData>
